--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
           <t>DOI link</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Citations (Semantic Scholar)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -472,6 +477,9 @@
           <t>https://doi.org/10.3390/nu12061878</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -498,6 +506,9 @@
           <t>https://doi.org/10.1136/bmjopen-2021-054839</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -524,6 +535,9 @@
           <t>https://doi.org/10.3390/nu14142866</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -549,6 +563,9 @@
         <is>
           <t>https://doi.org/10.1101/2025.09.18.25333312</t>
         </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
